--- a/artfynd/A 46145-2024 artfynd.xlsx
+++ b/artfynd/A 46145-2024 artfynd.xlsx
@@ -2434,10 +2434,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120285909</v>
+        <v>120285912</v>
       </c>
       <c r="B19" t="n">
-        <v>90972</v>
+        <v>90598</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2450,16 +2450,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6040186</v>
+        <v>5432</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2469,10 +2474,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>768904</v>
+        <v>769155</v>
       </c>
       <c r="R19" t="n">
-        <v>7084510</v>
+        <v>7084633</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2531,10 +2536,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120285908</v>
+        <v>120285909</v>
       </c>
       <c r="B20" t="n">
-        <v>87423</v>
+        <v>90972</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2547,21 +2552,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4412</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Äggvaxskivling</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2571,10 +2571,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>768925</v>
+        <v>768904</v>
       </c>
       <c r="R20" t="n">
-        <v>7084222</v>
+        <v>7084510</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2633,10 +2633,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120285912</v>
+        <v>120285908</v>
       </c>
       <c r="B21" t="n">
-        <v>90598</v>
+        <v>87423</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2649,21 +2649,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>4412</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>769155</v>
+        <v>768925</v>
       </c>
       <c r="R21" t="n">
-        <v>7084633</v>
+        <v>7084222</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 46145-2024 artfynd.xlsx
+++ b/artfynd/A 46145-2024 artfynd.xlsx
@@ -2434,10 +2434,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120285912</v>
+        <v>120285909</v>
       </c>
       <c r="B19" t="n">
-        <v>90598</v>
+        <v>90972</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2450,21 +2450,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2474,10 +2469,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>769155</v>
+        <v>768904</v>
       </c>
       <c r="R19" t="n">
-        <v>7084633</v>
+        <v>7084510</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2536,10 +2531,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120285909</v>
+        <v>120285912</v>
       </c>
       <c r="B20" t="n">
-        <v>90972</v>
+        <v>90598</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2552,16 +2547,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6040186</v>
+        <v>5432</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2571,10 +2571,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>768904</v>
+        <v>769155</v>
       </c>
       <c r="R20" t="n">
-        <v>7084510</v>
+        <v>7084633</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 46145-2024 artfynd.xlsx
+++ b/artfynd/A 46145-2024 artfynd.xlsx
@@ -2434,10 +2434,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120285909</v>
+        <v>120285912</v>
       </c>
       <c r="B19" t="n">
-        <v>90972</v>
+        <v>90598</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2450,16 +2450,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6040186</v>
+        <v>5432</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2469,10 +2474,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>768904</v>
+        <v>769155</v>
       </c>
       <c r="R19" t="n">
-        <v>7084510</v>
+        <v>7084633</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2531,10 +2536,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120285912</v>
+        <v>120285908</v>
       </c>
       <c r="B20" t="n">
-        <v>90598</v>
+        <v>87423</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2547,21 +2552,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>4412</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2571,10 +2576,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>769155</v>
+        <v>768925</v>
       </c>
       <c r="R20" t="n">
-        <v>7084633</v>
+        <v>7084222</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2633,10 +2638,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120285908</v>
+        <v>120285909</v>
       </c>
       <c r="B21" t="n">
-        <v>87423</v>
+        <v>90972</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2649,21 +2654,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4412</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Äggvaxskivling</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>768925</v>
+        <v>768904</v>
       </c>
       <c r="R21" t="n">
-        <v>7084222</v>
+        <v>7084510</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
